--- a/ExcelToJSONConverter/excel/region.xlsx
+++ b/ExcelToJSONConverter/excel/region.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18CF0C75-BC11-4ADD-A646-EE1CC1C9CFD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94327EB2-42C8-428B-9ABA-FF149B1D5A94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20325" yWindow="1515" windowWidth="16200" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-17505" yWindow="3075" windowWidth="16200" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -133,23 +133,23 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>WEI</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SHU</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>WU</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>CaoCao</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>SunQuan</t>
+  </si>
+  <si>
+    <t>Wu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wei</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -727,13 +727,13 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
         <v>23</v>
@@ -744,7 +744,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>15</v>
@@ -767,7 +767,7 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
         <v>25</v>
